--- a/data/gravel/Chumba Sendero Ti 2025.xlsx
+++ b/data/gravel/Chumba Sendero Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6D0099-8377-4E4C-AE2B-9B94F68E93AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CA9B20-466F-D846-B8B0-5B915FF99512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27100" yWindow="-25560" windowWidth="34140" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,9 +167,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>steel</t>
-  </si>
-  <si>
     <t>udh</t>
   </si>
   <si>
@@ -408,6 +405,9 @@
   </si>
   <si>
     <t>my estimates are ~ 530 so these measures are with 0% sag</t>
+  </si>
+  <si>
+    <t>titanium</t>
   </si>
 </sst>
 </file>
@@ -788,7 +788,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -812,7 +812,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -820,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -828,43 +828,43 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>81</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>82</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>83</v>
-      </c>
-      <c r="F8" t="s">
-        <v>84</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>8</v>
@@ -965,7 +965,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12">
         <v>74.8</v>
@@ -998,23 +998,40 @@
         <v>17</v>
       </c>
       <c r="C13">
+        <f>H13*25.4</f>
+        <v>393.7</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13:G13" si="0">I13*25.4</f>
+        <v>412.75</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>438.15</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>463.54999999999995</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>514.35</v>
+      </c>
+      <c r="H13">
         <v>15.5</v>
       </c>
-      <c r="D13">
+      <c r="I13">
         <v>16.25</v>
       </c>
-      <c r="E13">
+      <c r="J13">
         <v>17.25</v>
       </c>
-      <c r="F13">
+      <c r="K13">
         <v>18.25</v>
       </c>
-      <c r="G13">
+      <c r="L13">
         <v>20.25</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1032,35 +1049,35 @@
         <v>420</v>
       </c>
       <c r="D14">
-        <f t="shared" ref="D14:G14" si="0">VALUE(LEFT(I14,3))</f>
+        <f t="shared" ref="D14:G14" si="1">VALUE(LEFT(I14,3))</f>
         <v>420</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>420</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>420</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>428</v>
       </c>
       <c r="H14" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" t="s">
         <v>107</v>
-      </c>
-      <c r="I14" t="s">
-        <v>107</v>
-      </c>
-      <c r="J14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" t="s">
-        <v>107</v>
-      </c>
-      <c r="L14" t="s">
-        <v>108</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -1109,35 +1126,35 @@
         <v>1118</v>
       </c>
       <c r="D16">
-        <f t="shared" ref="D16:G16" si="1">VALUE(LEFT(I16,4))</f>
+        <f t="shared" ref="D16:G16" si="2">VALUE(LEFT(I16,4))</f>
         <v>1141</v>
       </c>
       <c r="E16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1156</v>
       </c>
       <c r="F16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1167</v>
       </c>
       <c r="G16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1206</v>
       </c>
       <c r="H16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" t="s">
         <v>109</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>110</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>111</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>112</v>
-      </c>
-      <c r="L16" t="s">
-        <v>113</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1152,23 +1169,40 @@
         <v>25</v>
       </c>
       <c r="C17">
+        <f>H17*25.4</f>
+        <v>749.3</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17:G17" si="3">I17*25.4</f>
+        <v>762</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="3"/>
+        <v>782.31999999999994</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>800.09999999999991</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>838.19999999999993</v>
+      </c>
+      <c r="H17">
         <v>29.5</v>
       </c>
-      <c r="D17">
+      <c r="I17">
         <v>30</v>
       </c>
-      <c r="E17">
+      <c r="J17">
         <v>30.8</v>
       </c>
-      <c r="F17">
+      <c r="K17">
         <v>31.5</v>
       </c>
-      <c r="G17">
+      <c r="L17">
         <v>33</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -1206,10 +1240,10 @@
     </row>
     <row r="19" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C19">
         <v>702</v>
@@ -1266,10 +1300,10 @@
     </row>
     <row r="21" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C21">
         <v>230</v>
@@ -1314,7 +1348,7 @@
         <v>530</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1344,7 +1378,7 @@
         <v>44</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -1356,7 +1390,7 @@
     </row>
     <row r="24" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -1489,19 +1523,19 @@
         <v>152.4</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:G33" si="2">D34*2.54</f>
+        <f t="shared" ref="D32:G33" si="4">D34*2.54</f>
         <v>170.18</v>
       </c>
       <c r="E32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175.26</v>
       </c>
       <c r="F32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>180.34</v>
       </c>
       <c r="G32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>187.96</v>
       </c>
     </row>
@@ -1514,19 +1548,19 @@
         <v>170.18</v>
       </c>
       <c r="D33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175.26</v>
       </c>
       <c r="E33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>177.8</v>
       </c>
       <c r="F33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>185.42000000000002</v>
       </c>
       <c r="G33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>193.04</v>
       </c>
     </row>
@@ -1572,83 +1606,83 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" t="s">
         <v>92</v>
       </c>
-      <c r="B36" t="s">
-        <v>93</v>
-      </c>
       <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" t="s">
         <v>100</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" t="s">
         <v>87</v>
       </c>
-      <c r="E36" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" t="s">
-        <v>102</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
-      </c>
       <c r="H36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" t="s">
         <v>104</v>
       </c>
-      <c r="D37" t="s">
+      <c r="G37" t="s">
         <v>104</v>
       </c>
-      <c r="E37" t="s">
-        <v>104</v>
-      </c>
-      <c r="F37" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" t="s">
-        <v>105</v>
-      </c>
       <c r="H37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>43</v>
       </c>
-      <c r="B39" t="s">
-        <v>44</v>
+      <c r="B39" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41">
         <v>20</v>
@@ -1656,7 +1690,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42">
         <v>2.4</v>
@@ -1664,12 +1698,12 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <v>120</v>
@@ -1677,7 +1711,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="1">
         <v>120</v>
@@ -1685,17 +1719,17 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>148</v>
@@ -1703,7 +1737,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49">
         <v>110</v>
@@ -1711,20 +1745,20 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52">
         <v>31.6</v>
@@ -1732,13 +1766,13 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>38</v>
@@ -1746,53 +1780,53 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1800,7 +1834,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -1809,61 +1843,61 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70">
         <v>4450</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Chumba Sendero Ti 2025.xlsx
+++ b/data/gravel/Chumba Sendero Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CA9B20-466F-D846-B8B0-5B915FF99512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4A795F-0114-9F45-8DDA-176C9E9A6221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27100" yWindow="-25560" windowWidth="34140" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>titanium</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/1734790323833-9S8MGWMUHW1BQCD5ZGHX/Chumba-Sendero-MTB-Titanium-a.jpg?format=2500w</t>
   </si>
 </sst>
 </file>
@@ -815,6 +818,11 @@
         <v>97</v>
       </c>
     </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Chumba Sendero Ti 2025.xlsx
+++ b/data/gravel/Chumba Sendero Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4A795F-0114-9F45-8DDA-176C9E9A6221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB87CDE-5CA1-B642-A4D5-3A13EBDAB8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27100" yWindow="-25560" windowWidth="34140" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/1734790323833-9S8MGWMUHW1BQCD5ZGHX/Chumba-Sendero-MTB-Titanium-a.jpg?format=2500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri, USA</t>
   </si>
 </sst>
 </file>
@@ -772,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1908,6 +1914,14 @@
         <v>95</v>
       </c>
     </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Chumba Sendero Ti 2025.xlsx
+++ b/data/gravel/Chumba Sendero Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB87CDE-5CA1-B642-A4D5-3A13EBDAB8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991AFE80-E207-4846-AA76-1AF620033FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27100" yWindow="-25560" windowWidth="34140" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="134">
   <si>
     <t>brand</t>
   </si>
@@ -417,6 +417,24 @@
   </si>
   <si>
     <t>Kansas City, Missouri, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -778,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1749,7 +1767,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -1757,168 +1775,198 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>56</v>
       </c>
-      <c r="B52">
+      <c r="B58">
         <v>31.6</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="1"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>58</v>
       </c>
-      <c r="B54">
+      <c r="B60">
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>67</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>68</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B70">
-        <v>4450</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C70" s="1"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>75</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>4450</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>126</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>127</v>
       </c>
     </row>

--- a/data/gravel/Chumba Sendero Ti 2025.xlsx
+++ b/data/gravel/Chumba Sendero Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991AFE80-E207-4846-AA76-1AF620033FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251937B3-1071-4049-AB1D-42DF7ED53924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27100" yWindow="-25560" windowWidth="34140" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/Chumba Sendero Ti 2025.xlsx
+++ b/data/gravel/Chumba Sendero Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251937B3-1071-4049-AB1D-42DF7ED53924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8899BA-9A3A-DA47-88FA-2BF8D24678A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27100" yWindow="-25560" windowWidth="34140" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
   <si>
     <t>brand</t>
   </si>
@@ -305,9 +305,6 @@
     <t>external</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -323,9 +320,6 @@
     <t>USD</t>
   </si>
   <si>
-    <t>Sendero Ti</t>
-  </si>
-  <si>
     <t>https://chumbausa.com/sendero-titanium-custom-mountain-bike-29er</t>
   </si>
   <si>
@@ -401,9 +395,6 @@
     <t>frame only</t>
   </si>
   <si>
-    <t>a8:g33</t>
-  </si>
-  <si>
     <t>my estimates are ~ 530 so these measures are with 0% sag</t>
   </si>
   <si>
@@ -435,6 +426,27 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>Sendero Ti (short)</t>
+  </si>
+  <si>
+    <t>ZS44</t>
+  </si>
+  <si>
+    <t>EC44</t>
+  </si>
+  <si>
+    <t>120-130</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g34</t>
   </si>
 </sst>
 </file>
@@ -796,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -815,7 +827,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -839,12 +851,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -852,7 +864,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -878,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>79</v>
@@ -997,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C12">
         <v>74.8</v>
@@ -1097,19 +1109,19 @@
         <v>428</v>
       </c>
       <c r="H14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -1174,19 +1186,19 @@
         <v>1206</v>
       </c>
       <c r="H16" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" t="s">
+        <v>107</v>
+      </c>
+      <c r="J16" t="s">
         <v>108</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>109</v>
       </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>110</v>
-      </c>
-      <c r="K16" t="s">
-        <v>111</v>
-      </c>
-      <c r="L16" t="s">
-        <v>112</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1272,10 +1284,10 @@
     </row>
     <row r="19" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C19">
         <v>702</v>
@@ -1332,10 +1344,10 @@
     </row>
     <row r="21" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C21">
         <v>230</v>
@@ -1380,7 +1392,7 @@
         <v>530</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1410,7 +1422,7 @@
         <v>44</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -1422,8 +1434,24 @@
     </row>
     <row r="24" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>90</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C24">
+        <v>120</v>
+      </c>
+      <c r="D24">
+        <v>120</v>
+      </c>
+      <c r="E24">
+        <v>120</v>
+      </c>
+      <c r="F24">
+        <v>120</v>
+      </c>
+      <c r="G24">
+        <v>120</v>
+      </c>
+      <c r="H24" s="1"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -1432,103 +1460,110 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
+    <row r="25" spans="1:16" ht="21" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27">
-        <v>50</v>
-      </c>
-      <c r="D27">
-        <v>50</v>
-      </c>
-      <c r="E27">
-        <v>50</v>
-      </c>
-      <c r="F27">
-        <v>50</v>
-      </c>
-      <c r="G27">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>50</v>
+      </c>
+      <c r="D28">
+        <v>50</v>
+      </c>
+      <c r="E28">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <v>50</v>
+      </c>
+      <c r="G28">
+        <v>60</v>
+      </c>
+      <c r="H28" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" t="s">
+        <v>101</v>
+      </c>
+      <c r="J28" t="s">
+        <v>101</v>
+      </c>
+      <c r="K28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L28" t="s">
+        <v>102</v>
+      </c>
+      <c r="M28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>35</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <f>4/2.205*1000</f>
         <v>1814.0589569160995</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29">
-        <v>700</v>
-      </c>
-      <c r="D29">
-        <v>700</v>
-      </c>
-      <c r="E29">
-        <v>700</v>
-      </c>
-      <c r="F29">
-        <v>700</v>
-      </c>
-      <c r="G29">
-        <v>700</v>
-      </c>
-    </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="G30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>2.4</v>
@@ -1548,426 +1583,437 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>2.4</v>
+      </c>
+      <c r="D32">
+        <v>2.4</v>
+      </c>
+      <c r="E32">
+        <v>2.4</v>
+      </c>
+      <c r="F32">
+        <v>2.4</v>
+      </c>
+      <c r="G32">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
-        <v>152.4</v>
-      </c>
-      <c r="D32">
-        <f t="shared" ref="D32:G33" si="4">D34*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
+        <v>165.1</v>
+      </c>
+      <c r="D33">
+        <f t="shared" ref="D33:G34" si="4">D35*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <f t="shared" si="4"/>
         <v>175.26</v>
       </c>
-      <c r="F32">
+      <c r="F33">
         <f t="shared" si="4"/>
         <v>180.34</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <f t="shared" si="4"/>
         <v>187.96</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="C33">
-        <f>C35*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <f t="shared" si="4"/>
         <v>175.26</v>
       </c>
-      <c r="E33">
+      <c r="E34">
         <f t="shared" si="4"/>
         <v>177.8</v>
       </c>
-      <c r="F33">
+      <c r="F34">
         <f t="shared" si="4"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="G33">
+      <c r="G34">
         <f t="shared" si="4"/>
         <v>193.04</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C34">
-        <v>60</v>
-      </c>
-      <c r="D34">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C35">
+        <v>65</v>
+      </c>
+      <c r="D35">
         <v>67</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <v>69</v>
       </c>
-      <c r="F34">
+      <c r="F35">
         <v>71</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35">
-        <v>67</v>
-      </c>
-      <c r="D35">
-        <v>69</v>
-      </c>
-      <c r="E35">
-        <v>70</v>
-      </c>
-      <c r="F35">
-        <v>73</v>
-      </c>
-      <c r="G35">
-        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" t="s">
-        <v>100</v>
-      </c>
-      <c r="F36" t="s">
-        <v>101</v>
-      </c>
-      <c r="G36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H36" t="s">
-        <v>85</v>
+        <v>42</v>
+      </c>
+      <c r="C36">
+        <v>67</v>
+      </c>
+      <c r="D36">
+        <v>69</v>
+      </c>
+      <c r="E36">
+        <v>70</v>
+      </c>
+      <c r="F36">
+        <v>73</v>
+      </c>
+      <c r="G36">
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" t="s">
         <v>98</v>
       </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" t="s">
-        <v>103</v>
-      </c>
       <c r="F37" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G37" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41">
-        <v>20</v>
+        <v>44</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42">
-        <v>2.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="B43">
+        <v>2.4</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44">
-        <v>120</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="1">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="B46" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48">
-        <v>148</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>53</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58">
-        <v>31.6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60">
-        <v>38</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70" s="1"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
       <c r="C71" s="1"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>70</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76">
-        <v>4450</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>4450</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>76</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" t="s">
-        <v>127</v>
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>123</v>
+      </c>
+      <c r="B81" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
